--- a/Example/Extract Pandat Results/P-S.xlsx
+++ b/Example/Extract Pandat Results/P-S.xlsx
@@ -988,17 +988,26 @@
       <c r="E12">
         <v>90</v>
       </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
       <c r="G12">
         <v>10</v>
       </c>
       <c r="H12">
         <v>98.70140615</v>
       </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
       <c r="J12">
         <v>1.298593846</v>
       </c>
       <c r="K12">
         <v>90</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
       </c>
       <c r="M12">
         <v>10</v>
@@ -1029,17 +1038,26 @@
       <c r="F13">
         <v>10</v>
       </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
       <c r="H13">
         <v>96.79167732000001</v>
       </c>
       <c r="I13">
         <v>3.20832268</v>
       </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
       <c r="K13">
         <v>90</v>
       </c>
       <c r="L13">
         <v>10</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
       </c>
       <c r="N13">
         <v>0.001848691915</v>
@@ -1517,17 +1535,26 @@
       <c r="F23">
         <v>1</v>
       </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
       <c r="H23">
         <v>99.67668584</v>
       </c>
       <c r="I23">
         <v>0.3233141608</v>
       </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
       <c r="K23">
         <v>99</v>
       </c>
       <c r="L23">
         <v>1</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
       </c>
       <c r="N23">
         <v>0.001977321013</v>
@@ -1817,6 +1844,24 @@
       <c r="J29">
         <v>0.5641693102999999</v>
       </c>
+      <c r="K29">
+        <v>94</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29">
+        <v>5</v>
+      </c>
+      <c r="N29">
+        <v>0.001699859024</v>
+      </c>
+      <c r="O29">
+        <v>-0.0002479645794</v>
+      </c>
+      <c r="P29">
+        <v>-0.001451894444</v>
+      </c>
     </row>
     <row r="30" spans="1:16">
       <c r="A30">
@@ -1849,6 +1894,24 @@
       <c r="J30">
         <v>0.6882759985</v>
       </c>
+      <c r="K30">
+        <v>93</v>
+      </c>
+      <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="M30">
+        <v>6</v>
+      </c>
+      <c r="N30">
+        <v>0.00165975416</v>
+      </c>
+      <c r="O30">
+        <v>-0.0002105626927</v>
+      </c>
+      <c r="P30">
+        <v>-0.001449191467</v>
+      </c>
     </row>
     <row r="31" spans="1:16">
       <c r="A31">
@@ -1881,6 +1944,24 @@
       <c r="J31">
         <v>0.8168512652</v>
       </c>
+      <c r="K31">
+        <v>92</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
+      </c>
+      <c r="M31">
+        <v>7</v>
+      </c>
+      <c r="N31">
+        <v>0.001620443788</v>
+      </c>
+      <c r="O31">
+        <v>-0.0001826328399</v>
+      </c>
+      <c r="P31">
+        <v>-0.001437810948</v>
+      </c>
     </row>
     <row r="32" spans="1:16">
       <c r="A32">
@@ -1913,6 +1994,24 @@
       <c r="J32">
         <v>0.9502043671</v>
       </c>
+      <c r="K32">
+        <v>91</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+      <c r="M32">
+        <v>8</v>
+      </c>
+      <c r="N32">
+        <v>0.001581999352</v>
+      </c>
+      <c r="O32">
+        <v>-0.0001609488047</v>
+      </c>
+      <c r="P32">
+        <v>-0.001421050548</v>
+      </c>
     </row>
     <row r="33" spans="1:16">
       <c r="A33">
@@ -1930,17 +2029,26 @@
       <c r="E33">
         <v>99</v>
       </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33">
         <v>99.88713254</v>
       </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
       <c r="J33">
         <v>0.1128674564</v>
       </c>
       <c r="K33">
         <v>99</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
       </c>
       <c r="M33">
         <v>1</v>
@@ -1983,6 +2091,24 @@
       <c r="J34">
         <v>1.088648565</v>
       </c>
+      <c r="K34">
+        <v>90</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
+      <c r="M34">
+        <v>9</v>
+      </c>
+      <c r="N34">
+        <v>0.001544521883</v>
+      </c>
+      <c r="O34">
+        <v>-0.0001436110989</v>
+      </c>
+      <c r="P34">
+        <v>-0.001400910784</v>
+      </c>
     </row>
     <row r="35" spans="1:16">
       <c r="A35">
@@ -2015,6 +2141,24 @@
       <c r="J35">
         <v>1.232501996</v>
       </c>
+      <c r="K35">
+        <v>89</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+      <c r="M35">
+        <v>10</v>
+      </c>
+      <c r="N35">
+        <v>0.001508112238</v>
+      </c>
+      <c r="O35">
+        <v>-0.0001294270847</v>
+      </c>
+      <c r="P35">
+        <v>-0.001378685153</v>
+      </c>
     </row>
     <row r="36" spans="1:16">
       <c r="A36">
@@ -2035,17 +2179,26 @@
       <c r="F36">
         <v>2</v>
       </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
       <c r="H36">
         <v>99.35666367</v>
       </c>
       <c r="I36">
         <v>0.6433363253</v>
       </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
       <c r="K36">
         <v>98</v>
       </c>
       <c r="L36">
         <v>2</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
       </c>
       <c r="N36">
         <v>0.001976573405</v>
@@ -2420,17 +2573,26 @@
       <c r="E44">
         <v>98</v>
       </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
       <c r="G44">
         <v>2</v>
       </c>
       <c r="H44">
         <v>99.77136971</v>
       </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
       <c r="J44">
         <v>0.2286302903</v>
       </c>
       <c r="K44">
         <v>98</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
       </c>
       <c r="M44">
         <v>2</v>
@@ -2573,6 +2735,24 @@
       <c r="J47">
         <v>1.168445848</v>
       </c>
+      <c r="K47">
+        <v>88</v>
+      </c>
+      <c r="L47">
+        <v>2</v>
+      </c>
+      <c r="M47">
+        <v>10</v>
+      </c>
+      <c r="N47">
+        <v>0.001617986541</v>
+      </c>
+      <c r="O47">
+        <v>-0.0002547938892</v>
+      </c>
+      <c r="P47">
+        <v>-0.001363192652</v>
+      </c>
     </row>
     <row r="48" spans="1:16">
       <c r="A48">
@@ -2593,17 +2773,26 @@
       <c r="F48">
         <v>3</v>
       </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
       <c r="H48">
         <v>99.03883934</v>
       </c>
       <c r="I48">
         <v>0.9611606575</v>
       </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
       <c r="K48">
         <v>97</v>
       </c>
       <c r="L48">
         <v>3</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
       </c>
       <c r="N48">
         <v>0.001971797478</v>
@@ -2928,17 +3117,26 @@
       <c r="E55">
         <v>97</v>
       </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
       <c r="G55">
         <v>3</v>
       </c>
       <c r="H55">
         <v>99.65238207</v>
       </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
       <c r="J55">
         <v>0.3476179302</v>
       </c>
       <c r="K55">
         <v>97</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
       </c>
       <c r="M55">
         <v>3</v>
@@ -3169,17 +3367,26 @@
       <c r="F60">
         <v>4</v>
       </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
       <c r="H60">
         <v>98.72216223</v>
       </c>
       <c r="I60">
         <v>1.277837767</v>
       </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
       <c r="K60">
         <v>96</v>
       </c>
       <c r="L60">
         <v>4</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
       </c>
       <c r="N60">
         <v>0.001963265188</v>
@@ -3454,17 +3661,26 @@
       <c r="E66">
         <v>96</v>
       </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
       <c r="G66">
         <v>4</v>
       </c>
       <c r="H66">
         <v>99.52984127000001</v>
       </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
       <c r="J66">
         <v>0.470158735</v>
       </c>
       <c r="K66">
         <v>96</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
       </c>
       <c r="M66">
         <v>4</v>
@@ -3745,17 +3961,26 @@
       <c r="F72">
         <v>5</v>
       </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
       <c r="H72">
         <v>98.40562126</v>
       </c>
       <c r="I72">
         <v>1.594378744</v>
       </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
       <c r="K72">
         <v>95</v>
       </c>
       <c r="L72">
         <v>5</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
       </c>
       <c r="N72">
         <v>0.001951187434</v>
@@ -3980,17 +4205,26 @@
       <c r="E77">
         <v>95</v>
       </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
       <c r="G77">
         <v>5</v>
       </c>
       <c r="H77">
         <v>99.40341868</v>
       </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
       <c r="J77">
         <v>0.5965813226</v>
       </c>
       <c r="K77">
         <v>95</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
       </c>
       <c r="M77">
         <v>5</v>
@@ -4321,17 +4555,26 @@
       <c r="F84">
         <v>6</v>
       </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
       <c r="H84">
         <v>98.08823954</v>
       </c>
       <c r="I84">
         <v>1.911760456</v>
       </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
       <c r="K84">
         <v>94</v>
       </c>
       <c r="L84">
         <v>6</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
       </c>
       <c r="N84">
         <v>0.001935786003</v>
@@ -4506,17 +4749,26 @@
       <c r="E88">
         <v>94</v>
       </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
       <c r="G88">
         <v>6</v>
       </c>
       <c r="H88">
         <v>99.27278418</v>
       </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
       <c r="J88">
         <v>0.727215823</v>
       </c>
       <c r="K88">
         <v>94</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
       </c>
       <c r="M88">
         <v>6</v>
@@ -4897,17 +5149,26 @@
       <c r="F96">
         <v>7</v>
       </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
       <c r="H96">
         <v>97.76906946</v>
       </c>
       <c r="I96">
         <v>2.23093054</v>
       </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
       <c r="K96">
         <v>93</v>
       </c>
       <c r="L96">
         <v>7</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
       </c>
       <c r="N96">
         <v>0.001917513317</v>
@@ -5032,17 +5293,26 @@
       <c r="E99">
         <v>93</v>
       </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
       <c r="G99">
         <v>7</v>
       </c>
       <c r="H99">
         <v>99.13760492</v>
       </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
       <c r="J99">
         <v>0.8623950789</v>
       </c>
       <c r="K99">
         <v>93</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
       </c>
       <c r="M99">
         <v>7</v>
@@ -5473,17 +5743,26 @@
       <c r="F108">
         <v>8</v>
       </c>
+      <c r="G108">
+        <v>0</v>
+      </c>
       <c r="H108">
         <v>97.44718718999999</v>
       </c>
       <c r="I108">
         <v>2.552812808</v>
       </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
       <c r="K108">
         <v>92</v>
       </c>
       <c r="L108">
         <v>8</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
       </c>
       <c r="N108">
         <v>0.001896671102</v>
@@ -5558,17 +5837,26 @@
       <c r="E110">
         <v>92</v>
       </c>
+      <c r="F110">
+        <v>0</v>
+      </c>
       <c r="G110">
         <v>8</v>
       </c>
       <c r="H110">
         <v>98.99754424</v>
       </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
       <c r="J110">
         <v>1.002455764</v>
       </c>
       <c r="K110">
         <v>92</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
       </c>
       <c r="M110">
         <v>8</v>
@@ -6049,17 +6337,26 @@
       <c r="F120">
         <v>9</v>
       </c>
+      <c r="G120">
+        <v>0</v>
+      </c>
       <c r="H120">
         <v>97.12168737</v>
       </c>
       <c r="I120">
         <v>2.878312635</v>
       </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
       <c r="K120">
         <v>91</v>
       </c>
       <c r="L120">
         <v>9</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
       </c>
       <c r="N120">
         <v>0.001873613441</v>
@@ -6084,17 +6381,26 @@
       <c r="E121">
         <v>91</v>
       </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
       <c r="G121">
         <v>9</v>
       </c>
       <c r="H121">
         <v>98.85226050999999</v>
       </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
       <c r="J121">
         <v>1.147739489</v>
       </c>
       <c r="K121">
         <v>91</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
       </c>
       <c r="M121">
         <v>9</v>
@@ -6122,11 +6428,29 @@
       <c r="E122">
         <v>100</v>
       </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
       <c r="H122">
         <v>100</v>
       </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
       <c r="K122">
         <v>100</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
       </c>
       <c r="N122">
         <v>0</v>
